--- a/event_planner_forms/002_event_feedback_form--event_planner_forms.xlsx
+++ b/event_planner_forms/002_event_feedback_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'not_satisfied',_'text':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'not_satisfied', 'text': 'Not Satisfied'}</t>
+          <t>not satisfied</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_satisfied',_'text':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_satisfied', 'text': 'Somewhat Satisfied'}</t>
+          <t>somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'very_satisfied',_'text':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'very_satisfied', 'text': 'Very Satisfied'}</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'venue',_'text':_'venue'}</t>
+          <t>venue</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'venue', 'text': 'Venue'}</t>
+          <t>venue</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'presentation',_'text':_'presentation'}</t>
+          <t>presentation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'presentation', 'text': 'Presentation'}</t>
+          <t>presentation</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'speakers',_'text':_'speakers'}</t>
+          <t>speakers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'speakers', 'text': 'Speakers'}</t>
+          <t>speakers</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'catering',_'text':_'catering'}</t>
+          <t>catering</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'catering', 'text': 'Catering'}</t>
+          <t>catering</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'overall',_'text':_'overall'}</t>
+          <t>overall</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'overall', 'text': 'Overall'}</t>
+          <t>overall</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'logistics',_'text':_'logistics'}</t>
+          <t>logistics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'logistics', 'text': 'Logistics'}</t>
+          <t>logistics</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'agree',_'text':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'agree', 'text': 'Agree'}</t>
+          <t>agree</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'not_agree',_'text':_'not_agree'}</t>
+          <t>not_agree</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'not_agree', 'text': 'Not Agree'}</t>
+          <t>not agree</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'neutral',_'text':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'neutral', 'text': 'Neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'agree',_'text':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'agree', 'text': 'Agree'}</t>
+          <t>agree</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'not_agree',_'text':_'not_agree'}</t>
+          <t>not_agree</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'not_agree', 'text': 'Not Agree'}</t>
+          <t>not agree</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'neutral',_'text':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'neutral', 'text': 'Neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'venue',_'text':_'venue'}</t>
+          <t>venue</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'venue', 'text': 'Venue'}</t>
+          <t>venue</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'not_venue',_'text':_'not_venue'}</t>
+          <t>not_venue</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'not_venue', 'text': 'Not Venue'}</t>
+          <t>not venue</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'neutral',_'text':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'neutral', 'text': 'Neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
